--- a/outputs_xlsx_solution/test_new3.4-wide-NR-4.xlsx
+++ b/outputs_xlsx_solution/test_new3.4-wide-NR-4.xlsx
@@ -80,6 +80,9 @@
     <t>EX</t>
   </si>
   <si>
+    <t>FU Stall</t>
+  </si>
+  <si>
     <t>fadd F4, F1, F1</t>
   </si>
   <si>
@@ -156,6 +159,9 @@
   </si>
   <si>
     <t>Common Data Bus Stall (stalled because the CDB bandwidth is saturated)</t>
+  </si>
+  <si>
+    <t>Functional Unit Stall (stalled because the functional unit is busy)</t>
   </si>
 </sst>
 </file>
@@ -684,7 +690,7 @@
         <v>14</v>
       </c>
       <c r="G2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
@@ -704,13 +710,13 @@
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G3" t="s">
         <v>14</v>
       </c>
       <c r="H3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
@@ -730,13 +736,16 @@
         <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="G4" t="s">
+        <v>15</v>
       </c>
       <c r="H4" t="s">
         <v>14</v>
       </c>
       <c r="I4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
@@ -756,13 +765,19 @@
         <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="G5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" t="s">
+        <v>15</v>
       </c>
       <c r="I5" t="s">
         <v>14</v>
       </c>
       <c r="J5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
@@ -785,10 +800,10 @@
         <v>14</v>
       </c>
       <c r="H6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7">
@@ -808,10 +823,10 @@
         <v>9</v>
       </c>
       <c r="G7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I7" t="s">
         <v>14</v>
@@ -823,7 +838,7 @@
         <v>14</v>
       </c>
       <c r="L7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8">
@@ -843,10 +858,10 @@
         <v>9</v>
       </c>
       <c r="H8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J8" t="s">
         <v>14</v>
@@ -858,7 +873,7 @@
         <v>14</v>
       </c>
       <c r="M8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
@@ -878,10 +893,10 @@
         <v>9</v>
       </c>
       <c r="I9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M9" t="s">
         <v>14</v>
@@ -896,7 +911,7 @@
         <v>14</v>
       </c>
       <c r="Q9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10">
@@ -907,17 +922,17 @@
         <v>32</v>
       </c>
       <c r="C10" t="s">
+        <v>16</v>
+      </c>
+      <c r="F10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G10" t="s">
+        <v>9</v>
+      </c>
+      <c r="J10" t="s">
         <v>15</v>
       </c>
-      <c r="F10" t="s">
-        <v>5</v>
-      </c>
-      <c r="G10" t="s">
-        <v>9</v>
-      </c>
-      <c r="J10" t="s">
-        <v>14</v>
-      </c>
       <c r="K10" t="s">
         <v>14</v>
       </c>
@@ -928,10 +943,10 @@
         <v>14</v>
       </c>
       <c r="N10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11">
@@ -942,7 +957,7 @@
         <v>36</v>
       </c>
       <c r="C11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F11" t="s">
         <v>5</v>
@@ -951,14 +966,14 @@
         <v>9</v>
       </c>
       <c r="J11" t="s">
+        <v>27</v>
+      </c>
+      <c r="K11" t="s">
+        <v>27</v>
+      </c>
+      <c r="L11" t="s">
         <v>26</v>
       </c>
-      <c r="K11" t="s">
-        <v>26</v>
-      </c>
-      <c r="L11" t="s">
-        <v>25</v>
-      </c>
       <c r="N11" t="s">
         <v>14</v>
       </c>
@@ -969,7 +984,7 @@
         <v>14</v>
       </c>
       <c r="Q11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12">
@@ -989,10 +1004,10 @@
         <v>9</v>
       </c>
       <c r="L12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q12" t="s">
         <v>14</v>
@@ -1007,7 +1022,7 @@
         <v>14</v>
       </c>
       <c r="U12" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
@@ -1018,7 +1033,7 @@
         <v>44</v>
       </c>
       <c r="C13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F13" t="s">
         <v>5</v>
@@ -1027,25 +1042,25 @@
         <v>9</v>
       </c>
       <c r="M13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q13" t="s">
         <v>14</v>
       </c>
       <c r="R13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="U13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14">
@@ -1056,7 +1071,7 @@
         <v>48</v>
       </c>
       <c r="C14" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G14" t="s">
         <v>5</v>
@@ -1068,10 +1083,10 @@
         <v>14</v>
       </c>
       <c r="R14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="U14" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15">
@@ -1082,7 +1097,7 @@
         <v>52</v>
       </c>
       <c r="C15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G15" t="s">
         <v>5</v>
@@ -1091,16 +1106,16 @@
         <v>9</v>
       </c>
       <c r="Q15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R15" t="s">
         <v>14</v>
       </c>
       <c r="S15" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="U15" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16">
@@ -1111,7 +1126,7 @@
         <v>56</v>
       </c>
       <c r="C16" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G16" t="s">
         <v>5</v>
@@ -1120,22 +1135,22 @@
         <v>9</v>
       </c>
       <c r="Q16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="U16" t="s">
         <v>14</v>
       </c>
       <c r="V16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
@@ -1146,7 +1161,7 @@
         <v>60</v>
       </c>
       <c r="C17" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G17" t="s">
         <v>5</v>
@@ -1155,13 +1170,13 @@
         <v>9</v>
       </c>
       <c r="U17" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="V17" t="s">
         <v>14</v>
       </c>
       <c r="W17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18">
@@ -1172,7 +1187,7 @@
         <v>36</v>
       </c>
       <c r="C18" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="W18" t="s">
         <v>5</v>
@@ -1190,7 +1205,7 @@
         <v>14</v>
       </c>
       <c r="AB18" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19">
@@ -1222,7 +1237,7 @@
         <v>14</v>
       </c>
       <c r="AC19" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20">
@@ -1233,7 +1248,7 @@
         <v>44</v>
       </c>
       <c r="C20" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="W20" t="s">
         <v>5</v>
@@ -1242,13 +1257,13 @@
         <v>9</v>
       </c>
       <c r="Y20" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AB20" t="s">
         <v>14</v>
       </c>
       <c r="AC20" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -1259,7 +1274,7 @@
         <v>48</v>
       </c>
       <c r="C21" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="W21" t="s">
         <v>5</v>
@@ -1271,10 +1286,10 @@
         <v>14</v>
       </c>
       <c r="Z21" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AC21" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22">
@@ -1285,7 +1300,7 @@
         <v>52</v>
       </c>
       <c r="C22" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X22" t="s">
         <v>5</v>
@@ -1294,16 +1309,16 @@
         <v>9</v>
       </c>
       <c r="Z22" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA22" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AB22" t="s">
         <v>14</v>
       </c>
       <c r="AC22" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23">
@@ -1314,7 +1329,7 @@
         <v>56</v>
       </c>
       <c r="C23" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X23" t="s">
         <v>5</v>
@@ -1323,13 +1338,13 @@
         <v>9</v>
       </c>
       <c r="AB23" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AC23" t="s">
         <v>14</v>
       </c>
       <c r="AD23" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24">
@@ -1340,7 +1355,7 @@
         <v>60</v>
       </c>
       <c r="C24" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="X24" t="s">
         <v>5</v>
@@ -1349,13 +1364,13 @@
         <v>9</v>
       </c>
       <c r="AC24" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AD24" t="s">
         <v>14</v>
       </c>
       <c r="AE24" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25">
@@ -1366,7 +1381,7 @@
         <v>36</v>
       </c>
       <c r="C25" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Y25" t="s">
         <v>5</v>
@@ -1384,7 +1399,7 @@
         <v>14</v>
       </c>
       <c r="AF25" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26">
@@ -1416,7 +1431,7 @@
         <v>14</v>
       </c>
       <c r="AG26" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27">
@@ -1427,7 +1442,7 @@
         <v>44</v>
       </c>
       <c r="C27" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Y27" t="s">
         <v>5</v>
@@ -1436,13 +1451,13 @@
         <v>9</v>
       </c>
       <c r="AD27" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AF27" t="s">
         <v>14</v>
       </c>
       <c r="AG27" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28">
@@ -1453,7 +1468,7 @@
         <v>48</v>
       </c>
       <c r="C28" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y28" t="s">
         <v>5</v>
@@ -1462,16 +1477,16 @@
         <v>9</v>
       </c>
       <c r="AD28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AE28" t="s">
         <v>14</v>
       </c>
       <c r="AF28" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AG28" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29">
@@ -1482,7 +1497,7 @@
         <v>52</v>
       </c>
       <c r="C29" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z29" t="s">
         <v>5</v>
@@ -1491,13 +1506,13 @@
         <v>9</v>
       </c>
       <c r="AE29" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF29" t="s">
         <v>14</v>
       </c>
       <c r="AG29" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="30">
@@ -1508,7 +1523,7 @@
         <v>56</v>
       </c>
       <c r="C30" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Z30" t="s">
         <v>5</v>
@@ -1517,13 +1532,13 @@
         <v>9</v>
       </c>
       <c r="AF30" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG30" t="s">
         <v>14</v>
       </c>
       <c r="AH30" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31">
@@ -1534,7 +1549,7 @@
         <v>60</v>
       </c>
       <c r="C31" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Z31" t="s">
         <v>5</v>
@@ -1543,13 +1558,13 @@
         <v>9</v>
       </c>
       <c r="AG31" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AH31" t="s">
         <v>14</v>
       </c>
       <c r="AI31" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="32">
@@ -1560,7 +1575,7 @@
         <v>36</v>
       </c>
       <c r="C32" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA32" t="s">
         <v>5</v>
@@ -1578,7 +1593,7 @@
         <v>14</v>
       </c>
       <c r="AJ32" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="33">
@@ -1610,7 +1625,7 @@
         <v>14</v>
       </c>
       <c r="AK33" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="34">
@@ -1621,7 +1636,7 @@
         <v>44</v>
       </c>
       <c r="C34" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA34" t="s">
         <v>5</v>
@@ -1630,13 +1645,13 @@
         <v>9</v>
       </c>
       <c r="AH34" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AJ34" t="s">
         <v>14</v>
       </c>
       <c r="AK34" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="35">
@@ -1647,7 +1662,7 @@
         <v>48</v>
       </c>
       <c r="C35" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA35" t="s">
         <v>5</v>
@@ -1656,16 +1671,16 @@
         <v>9</v>
       </c>
       <c r="AH35" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI35" t="s">
         <v>14</v>
       </c>
       <c r="AJ35" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AK35" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="36">
@@ -1676,7 +1691,7 @@
         <v>52</v>
       </c>
       <c r="C36" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AB36" t="s">
         <v>5</v>
@@ -1685,13 +1700,13 @@
         <v>9</v>
       </c>
       <c r="AI36" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AJ36" t="s">
         <v>14</v>
       </c>
       <c r="AK36" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="37">
@@ -1702,7 +1717,7 @@
         <v>56</v>
       </c>
       <c r="C37" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AB37" t="s">
         <v>5</v>
@@ -1711,13 +1726,13 @@
         <v>9</v>
       </c>
       <c r="AJ37" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK37" t="s">
         <v>14</v>
       </c>
       <c r="AL37" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="38">
@@ -1728,7 +1743,7 @@
         <v>60</v>
       </c>
       <c r="C38" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AB38" t="s">
         <v>5</v>
@@ -1737,13 +1752,13 @@
         <v>9</v>
       </c>
       <c r="AK38" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL38" t="s">
         <v>14</v>
       </c>
       <c r="AM38" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="39">
@@ -1754,7 +1769,7 @@
         <v>36</v>
       </c>
       <c r="C39" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AC39" t="s">
         <v>5</v>
@@ -1772,7 +1787,7 @@
         <v>14</v>
       </c>
       <c r="AN39" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="40">
@@ -1804,7 +1819,7 @@
         <v>14</v>
       </c>
       <c r="AO40" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="41">
@@ -1815,7 +1830,7 @@
         <v>44</v>
       </c>
       <c r="C41" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AC41" t="s">
         <v>5</v>
@@ -1824,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="AL41" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AN41" t="s">
         <v>14</v>
       </c>
       <c r="AO41" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="42">
@@ -1841,7 +1856,7 @@
         <v>48</v>
       </c>
       <c r="C42" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AC42" t="s">
         <v>5</v>
@@ -1850,16 +1865,16 @@
         <v>9</v>
       </c>
       <c r="AL42" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AM42" t="s">
         <v>14</v>
       </c>
       <c r="AN42" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AO42" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="43">
@@ -1870,7 +1885,7 @@
         <v>52</v>
       </c>
       <c r="C43" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AD43" t="s">
         <v>5</v>
@@ -1879,13 +1894,13 @@
         <v>9</v>
       </c>
       <c r="AM43" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AN43" t="s">
         <v>14</v>
       </c>
       <c r="AO43" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="44">
@@ -1896,7 +1911,7 @@
         <v>56</v>
       </c>
       <c r="C44" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AD44" t="s">
         <v>5</v>
@@ -1905,13 +1920,13 @@
         <v>9</v>
       </c>
       <c r="AN44" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO44" t="s">
         <v>14</v>
       </c>
       <c r="AP44" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="45">
@@ -1922,7 +1937,7 @@
         <v>60</v>
       </c>
       <c r="C45" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AD45" t="s">
         <v>5</v>
@@ -1931,13 +1946,13 @@
         <v>9</v>
       </c>
       <c r="AO45" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AP45" t="s">
         <v>14</v>
       </c>
       <c r="AQ45" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="46">
@@ -1948,7 +1963,7 @@
         <v>64</v>
       </c>
       <c r="C46" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ46" t="s">
         <v>5</v>
@@ -1966,7 +1981,7 @@
         <v>14</v>
       </c>
       <c r="AV46" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="47">
@@ -1998,7 +2013,7 @@
         <v>14</v>
       </c>
       <c r="AW47" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="48">
@@ -2009,7 +2024,7 @@
         <v>72</v>
       </c>
       <c r="C48" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ48" t="s">
         <v>5</v>
@@ -2018,13 +2033,13 @@
         <v>9</v>
       </c>
       <c r="AS48" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AV48" t="s">
         <v>14</v>
       </c>
       <c r="AW48" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="49">
@@ -2035,7 +2050,7 @@
         <v>76</v>
       </c>
       <c r="C49" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ49" t="s">
         <v>5</v>
@@ -2044,18 +2059,18 @@
         <v>9</v>
       </c>
       <c r="AS49" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AW49" t="s">
         <v>14</v>
       </c>
       <c r="AX49" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="52">
@@ -2063,7 +2078,7 @@
         <v>5</v>
       </c>
       <c r="B52" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="53">
@@ -2071,15 +2086,15 @@
         <v>9</v>
       </c>
       <c r="B53" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B54" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="55">
@@ -2087,39 +2102,55 @@
         <v>14</v>
       </c>
       <c r="B55" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B56" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B57" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B58" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
+        <v>21</v>
+      </c>
+      <c r="B59" t="s">
         <v>39</v>
       </c>
-      <c r="B59" t="s">
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
         <v>40</v>
+      </c>
+      <c r="B60" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>15</v>
+      </c>
+      <c r="B61" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
